--- a/docs/Birmarket_Test_Documentation.xlsx
+++ b/docs/Birmarket_Test_Documentation.xlsx
@@ -6626,7 +6626,7 @@
     <t xml:space="preserve">POJO</t>
   </si>
   <si>
-    <t xml:space="preserve">model/request (5) + model/response (13)</t>
+    <t xml:space="preserve">model/request (5) + model/response (14)</t>
   </si>
   <si>
     <t xml:space="preserve">Pul sahələri BigDecimal — float yuvarlaqlaşdırma xətası olmasın</t>
@@ -12365,159 +12365,159 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
